--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -5453,8 +5453,8 @@
       <c r="C114" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D114" s="6" t="s">
-        <v>103</v>
+      <c r="D114" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="E114" s="16" t="s">
         <v>145</v>
@@ -6572,7 +6572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="43">
         <v>8026646815</v>
       </c>
@@ -6582,8 +6582,8 @@
       <c r="C170" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D170" s="6" t="s">
-        <v>103</v>
+      <c r="D170" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E170" s="16" t="s">
         <v>41</v>
@@ -6749,7 +6749,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="43">
         <v>8018422112</v>
       </c>
@@ -6759,8 +6759,8 @@
       <c r="C179" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D179" s="6" t="s">
-        <v>103</v>
+      <c r="D179" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E179" s="16" t="s">
         <v>87</v>
@@ -10840,7 +10840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" s="43">
         <v>8047700799</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" s="43">
         <v>8047700402</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A387" s="43">
         <v>8048122287</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A388" s="43">
         <v>8045726238</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" s="43">
         <v>8048376758</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A391" s="41">
         <v>8048378017</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A392" s="43">
         <v>8048404709</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A393" s="43">
         <v>8048477713</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" s="43">
         <v>8048475657</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" s="43">
         <v>8048918959</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" s="43">
         <v>8048919825</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" s="43">
         <v>8048707235</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" s="43">
         <v>8048681239</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" s="43">
         <v>8048655431</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" s="43">
         <v>8049268498</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="402" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A402" s="43">
         <v>8049288637</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="403" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A403" s="43">
         <v>8049288826</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="404" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" s="43">
         <v>8049289184</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" s="43">
         <v>8047279970</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A406" s="43">
         <v>8050646155</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="407" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407" s="43">
         <v>8050011389</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="408" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" s="41">
         <v>8050305928</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" s="43">
         <v>8050526612</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="410" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" s="43">
         <v>8050527031</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" s="43">
         <v>8051285753</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A412" s="43">
         <v>8051441299</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" s="43">
         <v>8050997877</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" s="43">
         <v>8050997904</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="416" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" s="43">
         <v>8050998177</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A417" s="43">
         <v>8051033969</v>
       </c>
@@ -11517,7 +11517,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A418" s="41">
         <v>8051034378</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="E418" s="12"/>
       <c r="F418" s="12"/>
     </row>
-    <row r="419" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A419" s="43">
         <v>8051840591</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A420" s="43">
         <v>8051663676</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A421" s="43">
         <v>8052077176</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A422" s="43">
         <v>8052149936</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A423" s="43">
         <v>8052148564</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A425" s="43">
         <v>8048476917</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A426" s="43">
         <v>8052930447</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A427" s="43">
         <v>8052576162</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A428" s="43">
         <v>8053305246</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A429" s="43">
         <v>8053437617</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A430" s="43">
         <v>8054172185</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A431" s="43">
         <v>8053437638</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A432" s="43">
         <v>8053437575</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A433" s="43">
         <v>8053706924</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A434" s="43">
         <v>8054023518</v>
       </c>
@@ -11855,7 +11855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A435" s="43">
         <v>8054175945</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A436" s="43">
         <v>8054388660</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A437" s="43">
         <v>8054396581</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A438" s="43">
         <v>8054412730</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A439" s="43">
         <v>8054644939</v>
       </c>
@@ -11961,7 +11961,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A440" s="43">
         <v>8054612536</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A441" s="43">
         <v>8055020061</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A442" s="43">
         <v>8055481362</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A444" s="43">
         <v>8055369551</v>
       </c>
@@ -12076,7 +12076,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A445" s="43">
         <v>8055407944</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A446" s="43">
         <v>8055529514</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A447" s="43">
         <v>8056123966</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A448" s="41">
         <v>8056124191</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A449" s="43">
         <v>8056132000</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A450" s="43">
         <v>8056514788</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A451" s="43">
         <v>8056511542</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A452" s="43">
         <v>8056566599</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A453" s="43">
         <v>8056566661</v>
       </c>
@@ -12274,7 +12274,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A454" s="43">
         <v>8056566648</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A455" s="41">
         <v>8056865858</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A456" s="43">
         <v>8056866910</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A457" s="43">
         <v>8057098763</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A458" s="43">
         <v>8057205906</v>
       </c>
@@ -12378,7 +12378,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A459" s="43">
         <v>8057324598</v>
       </c>
@@ -12401,7 +12401,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A460" s="43">
         <v>8057342768</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A461" s="43">
         <v>8057342830</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A464" s="43">
         <v>8057522744</v>
       </c>
@@ -12507,7 +12507,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" s="43">
         <v>8057897454</v>
       </c>
@@ -12530,7 +12530,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="466" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" s="43">
         <v>8058031691</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="40.9" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A468" s="40">
         <v>8058168125</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="469" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A469" s="40">
         <v>8058165071</v>
       </c>
@@ -12616,12 +12616,12 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="470" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B470" s="2" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="471" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A471" s="43">
         <v>8059208023</v>
       </c>
@@ -12644,7 +12644,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="472" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A472" s="41">
         <v>8060089360</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="473" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" s="43">
         <v>8059631200</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="474" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" s="43">
         <v>8058331274</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="478" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" s="43">
         <v>8059671534</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" s="43">
         <v>8059671562</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="480" spans="1:8" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" s="43">
         <v>8058359012</v>
       </c>
@@ -12839,7 +12839,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A481" s="43">
         <v>8058331881</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A482" s="47">
         <v>8060089788</v>
       </c>
@@ -12873,7 +12873,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A483" s="43">
         <v>8063598278</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A484" s="43">
         <v>8059744378</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A486" s="43">
         <v>8063473184</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A487" s="43">
         <v>8063634168</v>
       </c>
@@ -12985,7 +12985,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" s="43">
         <v>8069662218</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A490" s="43">
         <v>8063968964</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A491" s="43">
         <v>8063969073</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A492" s="43">
         <v>8063969350</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A494" s="43">
         <v>8062565725</v>
       </c>
@@ -13131,7 +13131,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A495" s="43">
         <v>8062565902</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A496" s="44">
         <v>8062565978</v>
       </c>
@@ -13168,7 +13168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A497" s="43">
         <v>8062866234</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A498" s="43">
         <v>8062866352</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A499" s="43">
         <v>8062881987</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A500" s="44">
         <v>8062882079</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A502" s="43">
         <v>8063480640</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A503" s="43">
         <v>8064782612</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A505" s="43">
         <v>8064385288</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A508" s="43">
         <v>8058575114</v>
       </c>
@@ -13429,7 +13429,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A509" s="43">
         <v>8066986371</v>
       </c>
@@ -13452,7 +13452,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A510" s="43">
         <v>8066608888</v>
       </c>
@@ -13475,7 +13475,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A511" s="43">
         <v>8066609289</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A512" s="43">
         <v>8066577379</v>
       </c>
@@ -13521,7 +13521,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A513" s="43">
         <v>8063622970</v>
       </c>
@@ -13544,7 +13544,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A514" s="43">
         <v>8063622973</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A515" s="43">
         <v>8063622977</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A516" s="41">
         <v>8063622991</v>
       </c>
@@ -13602,7 +13602,7 @@
       <c r="E516" s="12"/>
       <c r="F516" s="12"/>
     </row>
-    <row r="517" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A517" s="43">
         <v>8065123058</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A518" s="43">
         <v>8065123410</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A520" s="43">
         <v>8035375831</v>
       </c>
@@ -13689,7 +13689,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A521" s="43">
         <v>8067627774</v>
       </c>
@@ -13712,7 +13712,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A522" s="41">
         <v>8067214396</v>
       </c>
@@ -13730,7 +13730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A523" s="43">
         <v>8067213750</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A524" s="43">
         <v>8067213220</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A526" s="43">
         <v>8067627213</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A529" s="43">
         <v>8067285527</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A530" s="43">
         <v>8067998699</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" s="43">
         <v>8068628364</v>
       </c>
@@ -13989,7 +13989,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A535" s="44">
         <v>8068940361</v>
       </c>
@@ -14006,7 +14006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A536" s="43">
         <v>8068940379</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A539" s="47">
         <v>8069664107</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A540" s="47">
         <v>8069663787</v>
       </c>
@@ -14105,7 +14105,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="542" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A542" s="47">
         <v>8068539251</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A543" s="43">
         <v>8068539793</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="546" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A546" s="47">
         <v>8065347267</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="551" spans="1:7" ht="20.45" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A551" s="44">
         <v>8069464155</v>
       </c>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3383" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="782">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2320,9 +2320,6 @@
     <t>Depois aumentar para 36</t>
   </si>
   <si>
-    <t>Tirar Duvida placas de 370 ??</t>
-  </si>
-  <si>
     <t>Repro</t>
   </si>
   <si>
@@ -2357,6 +2354,15 @@
   </si>
   <si>
     <t>1x3 W</t>
+  </si>
+  <si>
+    <t>Felipe Felizari</t>
+  </si>
+  <si>
+    <t>Jaime Germano Petry</t>
+  </si>
+  <si>
+    <t>Juliano Haag</t>
   </si>
 </sst>
 </file>
@@ -3034,7 +3040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I606"/>
+  <dimension ref="A1:I609"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -14113,7 +14119,7 @@
         <v>642</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>47</v>
@@ -14196,7 +14202,7 @@
         <v>645</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -14504,8 +14510,8 @@
       <c r="C561" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D561" s="6" t="s">
-        <v>22</v>
+      <c r="D561" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="E561" s="16" t="s">
         <v>322</v>
@@ -14829,10 +14835,13 @@
       <c r="C576" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E576" s="1" t="s">
+      <c r="D576" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E576" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F576" s="1" t="s">
+      <c r="F576" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G576" s="21" t="s">
@@ -14957,14 +14966,20 @@
       <c r="D582" s="1"/>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A583" s="47">
+      <c r="A583" s="44">
         <v>8070743765</v>
       </c>
-      <c r="B583" s="2" t="s">
+      <c r="B583" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="C583" s="2" t="s">
-        <v>767</v>
+      <c r="C583" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E583" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F583" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
@@ -14974,8 +14989,8 @@
       <c r="B584" s="10" t="s">
         <v>707</v>
       </c>
-      <c r="C584" s="10" t="s">
-        <v>19</v>
+      <c r="C584" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>765</v>
@@ -15273,13 +15288,13 @@
         <v>8073182347</v>
       </c>
       <c r="B601" s="10" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C601" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F601" s="1" t="s">
         <v>16</v>
@@ -15290,7 +15305,7 @@
         <v>8075397984</v>
       </c>
       <c r="B602" s="10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C602" s="10" t="s">
         <v>19</v>
@@ -15307,7 +15322,7 @@
         <v>8075507342</v>
       </c>
       <c r="B603" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C603" s="10" t="s">
         <v>19</v>
@@ -15324,7 +15339,7 @@
         <v>8075464594</v>
       </c>
       <c r="B604" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C604" s="10" t="s">
         <v>19</v>
@@ -15358,7 +15373,7 @@
         <v>8076036211</v>
       </c>
       <c r="B606" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C606" s="10" t="s">
         <v>19</v>
@@ -15368,6 +15383,21 @@
       </c>
       <c r="F606" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B607" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B608" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="609" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B609" s="2" t="s">
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -16402,7 +16432,7 @@
         <v>542</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="99" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -16552,7 +16582,7 @@
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C113" s="30" t="s">
         <v>542</v>
@@ -16563,7 +16593,7 @@
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="32" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C114" s="30" t="s">
         <v>542</v>
@@ -16571,7 +16601,7 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="32" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C115" s="30" t="s">
         <v>542</v>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -15254,7 +15254,7 @@
         <v>742</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E599" s="1" t="s">
         <v>55</v>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -15253,7 +15253,7 @@
       <c r="B599" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="C599" s="10" t="s">
+      <c r="C599" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E599" s="1" t="s">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="782">
   <si>
     <t>Protocolo</t>
   </si>
@@ -3040,7 +3040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I609"/>
+  <dimension ref="A1:I610"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -15247,19 +15247,20 @@
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A599" s="44">
+      <c r="A599" s="41">
         <v>8075220218</v>
       </c>
-      <c r="B599" s="10" t="s">
+      <c r="B599" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="C599" s="6" t="s">
+      <c r="C599" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E599" s="1" t="s">
+      <c r="D599" s="11"/>
+      <c r="E599" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F599" s="1" t="s">
+      <c r="F599" s="12" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15395,9 +15396,26 @@
         <v>780</v>
       </c>
     </row>
-    <row r="609" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B609" s="2" t="s">
         <v>781</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A610" s="44">
+        <v>8076260779</v>
+      </c>
+      <c r="B610" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="C610" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F610" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -14112,19 +14112,20 @@
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A542" s="47">
+      <c r="A542" s="41">
         <v>8068539251</v>
       </c>
-      <c r="B542" s="2" t="s">
+      <c r="B542" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="C542" s="2" t="s">
+      <c r="C542" s="11" t="s">
         <v>772</v>
       </c>
-      <c r="E542" s="1" t="s">
+      <c r="D542" s="11"/>
+      <c r="E542" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F542" s="1" t="s">
+      <c r="F542" s="12" t="s">
         <v>16</v>
       </c>
     </row>
@@ -14510,13 +14511,13 @@
       <c r="C561" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D561" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E561" s="16" t="s">
+      <c r="D561" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E561" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="F561" s="16" t="s">
+      <c r="F561" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3396" uniqueCount="783">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2363,6 +2363,9 @@
   </si>
   <si>
     <t>Juliano Haag</t>
+  </si>
+  <si>
+    <t>OBRA</t>
   </si>
 </sst>
 </file>
@@ -13164,8 +13167,8 @@
       <c r="B496" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="C496" s="10" t="s">
-        <v>19</v>
+      <c r="C496" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>47</v>
@@ -13244,14 +13247,14 @@
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A500" s="44">
+      <c r="A500" s="43">
         <v>8062882079</v>
       </c>
-      <c r="B500" s="10" t="s">
+      <c r="B500" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="C500" s="10" t="s">
-        <v>19</v>
+      <c r="C500" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>59</v>
@@ -13996,14 +13999,14 @@
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A535" s="44">
+      <c r="A535" s="43">
         <v>8068940361</v>
       </c>
-      <c r="B535" s="10" t="s">
+      <c r="B535" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="C535" s="10" t="s">
-        <v>19</v>
+      <c r="C535" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E535" s="19" t="s">
         <v>191</v>
@@ -14302,8 +14305,8 @@
       <c r="B551" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="C551" s="10" t="s">
-        <v>19</v>
+      <c r="C551" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>55</v>
@@ -14313,14 +14316,14 @@
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A552" s="44">
+      <c r="A552" s="43">
         <v>8069464653</v>
       </c>
-      <c r="B552" s="10" t="s">
+      <c r="B552" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="C552" s="10" t="s">
-        <v>19</v>
+      <c r="C552" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>222</v>
@@ -14422,14 +14425,14 @@
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A557" s="44">
+      <c r="A557" s="43">
         <v>8067939987</v>
       </c>
-      <c r="B557" s="10" t="s">
+      <c r="B557" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="C557" s="10" t="s">
-        <v>19</v>
+      <c r="C557" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>387</v>
@@ -14468,8 +14471,8 @@
       <c r="B559" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="C559" s="10" t="s">
-        <v>19</v>
+      <c r="C559" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>55</v>
@@ -14810,19 +14813,22 @@
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A575" s="44">
+      <c r="A575" s="43">
         <v>8072219805</v>
       </c>
-      <c r="B575" s="10" t="s">
+      <c r="B575" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="C575" s="10" t="s">
+      <c r="C575" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D575" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E575" s="1" t="s">
+      <c r="E575" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F575" s="1" t="s">
+      <c r="F575" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -14967,14 +14973,14 @@
       <c r="D582" s="1"/>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A583" s="44">
+      <c r="A583" s="43">
         <v>8070743765</v>
       </c>
-      <c r="B583" s="10" t="s">
+      <c r="B583" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="C583" s="10" t="s">
-        <v>19</v>
+      <c r="C583" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>778</v>
@@ -15008,7 +15014,7 @@
         <v>722</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>387</v>
@@ -15018,14 +15024,14 @@
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A586" s="44">
+      <c r="A586" s="43">
         <v>8067026818</v>
       </c>
-      <c r="B586" s="10" t="s">
+      <c r="B586" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="C586" s="10" t="s">
-        <v>19</v>
+      <c r="C586" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>422</v>
@@ -15035,14 +15041,14 @@
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A587" s="44">
+      <c r="A587" s="43">
         <v>8070577387</v>
       </c>
-      <c r="B587" s="10" t="s">
+      <c r="B587" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="C587" s="10" t="s">
-        <v>19</v>
+      <c r="C587" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>47</v>
@@ -15107,17 +15113,17 @@
       <c r="C590" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D590" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E590" s="16" t="s">
+      <c r="D590" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E590" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F590" s="16" t="s">
+      <c r="F590" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G590" s="22">
-        <v>46164</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
@@ -15130,33 +15136,36 @@
       <c r="C591" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D591" s="10" t="s">
+      <c r="D591" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E591" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F591" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G591" s="22">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A592" s="43">
+        <v>8073736149</v>
+      </c>
+      <c r="B592" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C592" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D592" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E591" s="16" t="s">
+      <c r="E592" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F591" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G591" s="22">
-        <v>46162</v>
-      </c>
-    </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A592" s="44">
-        <v>8073736149</v>
-      </c>
-      <c r="B592" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="C592" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E592" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F592" s="1" t="s">
+      <c r="F592" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15173,7 +15182,7 @@
         <v>761</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>387</v>
@@ -15206,14 +15215,14 @@
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A596" s="44">
+      <c r="A596" s="43">
         <v>8073784307</v>
       </c>
-      <c r="B596" s="10" t="s">
+      <c r="B596" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="C596" s="10" t="s">
-        <v>19</v>
+      <c r="C596" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>387</v>
@@ -15223,14 +15232,14 @@
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A597" s="44">
+      <c r="A597" s="43">
         <v>8073870779</v>
       </c>
-      <c r="B597" s="10" t="s">
+      <c r="B597" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C597" s="10" t="s">
-        <v>19</v>
+      <c r="C597" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>222</v>
@@ -15310,7 +15319,7 @@
         <v>774</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>19</v>
+        <v>782</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>387</v>
@@ -15320,14 +15329,14 @@
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A603" s="44">
+      <c r="A603" s="43">
         <v>8075507342</v>
       </c>
-      <c r="B603" s="10" t="s">
+      <c r="B603" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="C603" s="10" t="s">
-        <v>19</v>
+      <c r="C603" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E603" s="1" t="s">
         <v>222</v>
@@ -15337,14 +15346,14 @@
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A604" s="44">
+      <c r="A604" s="43">
         <v>8075464594</v>
       </c>
-      <c r="B604" s="10" t="s">
+      <c r="B604" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="C604" s="10" t="s">
-        <v>19</v>
+      <c r="C604" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E604" s="1" t="s">
         <v>47</v>
@@ -15354,14 +15363,14 @@
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A605" s="44">
+      <c r="A605" s="43">
         <v>8076034064</v>
       </c>
-      <c r="B605" s="10" t="s">
+      <c r="B605" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="C605" s="10" t="s">
-        <v>19</v>
+      <c r="C605" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>222</v>
@@ -15378,7 +15387,7 @@
         <v>777</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>19</v>
+        <v>782</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>55</v>
@@ -16470,6 +16479,9 @@
         <v>745</v>
       </c>
       <c r="C100" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D100" s="30" t="s">
         <v>542</v>
       </c>
     </row>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3396" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="787">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2359,13 +2359,25 @@
     <t>Felipe Felizari</t>
   </si>
   <si>
-    <t>Jaime Germano Petry</t>
-  </si>
-  <si>
-    <t>Juliano Haag</t>
-  </si>
-  <si>
     <t>OBRA</t>
+  </si>
+  <si>
+    <t>JAIME GERMANO PETRY</t>
+  </si>
+  <si>
+    <t>JULIANO HAAG</t>
+  </si>
+  <si>
+    <t>DJONATAN FORTUNATO</t>
+  </si>
+  <si>
+    <t>SERGIO LOCKS</t>
+  </si>
+  <si>
+    <t>MARIO FARIAS</t>
+  </si>
+  <si>
+    <t>ELTON IGNACZUK</t>
   </si>
 </sst>
 </file>
@@ -3043,7 +3055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I610"/>
+  <dimension ref="A1:I614"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -13004,13 +13016,13 @@
       <c r="C488" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D488" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E488" s="16" t="s">
+      <c r="D488" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E488" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F488" s="16" t="s">
+      <c r="F488" s="9" t="s">
         <v>295</v>
       </c>
     </row>
@@ -13965,8 +13977,8 @@
       <c r="C533" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D533" s="6" t="s">
-        <v>22</v>
+      <c r="D533" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="E533" s="16" t="s">
         <v>222</v>
@@ -14822,13 +14834,13 @@
       <c r="C575" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D575" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E575" s="16" t="s">
+      <c r="D575" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E575" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F575" s="16" t="s">
+      <c r="F575" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -14842,13 +14854,13 @@
       <c r="C576" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D576" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E576" s="16" t="s">
+      <c r="D576" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E576" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F576" s="16" t="s">
+      <c r="F576" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G576" s="21" t="s">
@@ -15319,7 +15331,7 @@
         <v>774</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>387</v>
@@ -15387,7 +15399,7 @@
         <v>777</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>55</v>
@@ -15402,13 +15414,19 @@
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A608" s="47">
+        <v>8076189679</v>
+      </c>
       <c r="B608" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A609" s="47">
+        <v>8076189717</v>
+      </c>
       <c r="B609" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
@@ -15426,6 +15444,38 @@
       </c>
       <c r="F610" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A611" s="47">
+        <v>8076298269</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A612" s="47">
+        <v>8076298033</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A613" s="47">
+        <v>8076291481</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A614" s="47">
+        <v>8076291122</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>786</v>
       </c>
     </row>
   </sheetData>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="787">
   <si>
     <t>Protocolo</t>
   </si>
@@ -14900,10 +14900,13 @@
       <c r="C578" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E578" s="1" t="s">
+      <c r="D578" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E578" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F578" s="1" t="s">
+      <c r="F578" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G578" s="22">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -14060,14 +14060,17 @@
       <c r="C537" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D537" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E537" s="16" t="s">
+      <c r="D537" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E537" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F537" s="16" t="s">
-        <v>16</v>
+      <c r="F537" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G537" s="22">
+        <v>46177</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3405" uniqueCount="790">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2378,6 +2378,15 @@
   </si>
   <si>
     <t>ELTON IGNACZUK</t>
+  </si>
+  <si>
+    <t>WALTER PREIS</t>
+  </si>
+  <si>
+    <t>MAILON KROCHMALNY</t>
+  </si>
+  <si>
+    <t>JONAS RENATO SENS</t>
   </si>
 </sst>
 </file>
@@ -3055,7 +3064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I614"/>
+  <dimension ref="A1:I617"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -14679,17 +14688,17 @@
       <c r="C568" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D568" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E568" s="16" t="s">
+      <c r="D568" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E568" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F568" s="16" t="s">
+      <c r="F568" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G568" s="22">
-        <v>46162</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
@@ -14748,14 +14757,17 @@
       <c r="C571" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D571" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E571" s="16" t="s">
+      <c r="D571" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E571" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F571" s="16" t="s">
-        <v>16</v>
+      <c r="F571" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G571" s="22">
+        <v>46168</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
@@ -14967,13 +14979,13 @@
       <c r="C581" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D581" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E581" s="16" t="s">
+      <c r="D581" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E581" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F581" s="16" t="s">
+      <c r="F581" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G581" s="22">
@@ -15313,14 +15325,14 @@
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A601" s="44">
+      <c r="A601" s="43">
         <v>8073182347</v>
       </c>
-      <c r="B601" s="10" t="s">
+      <c r="B601" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="C601" s="10" t="s">
-        <v>19</v>
+      <c r="C601" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E601" s="1" t="s">
         <v>778</v>
@@ -15436,19 +15448,22 @@
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A610" s="44">
+      <c r="A610" s="43">
         <v>8076260779</v>
       </c>
-      <c r="B610" s="10" t="s">
+      <c r="B610" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="C610" s="10" t="s">
+      <c r="C610" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D610" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E610" s="1" t="s">
+      <c r="E610" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F610" s="1" t="s">
+      <c r="F610" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15482,6 +15497,30 @@
       </c>
       <c r="B614" s="2" t="s">
         <v>786</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A615" s="47">
+        <v>8076953214</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A616" s="47">
+        <v>8076958269</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A617" s="47">
+        <v>8076958509</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>789</v>
       </c>
     </row>
   </sheetData>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -14475,13 +14475,13 @@
       <c r="C558" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D558" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E558" s="1" t="s">
+      <c r="D558" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E558" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F558" s="1" t="s">
+      <c r="F558" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G558" s="22">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3405" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="790">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15334,10 +15334,13 @@
       <c r="C601" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E601" s="1" t="s">
+      <c r="D601" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E601" s="16" t="s">
         <v>778</v>
       </c>
-      <c r="F601" s="1" t="s">
+      <c r="F601" s="16" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="790">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15503,11 +15503,20 @@
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A615" s="47">
+      <c r="A615" s="44">
         <v>8076953214</v>
       </c>
-      <c r="B615" s="2" t="s">
+      <c r="B615" s="10" t="s">
         <v>787</v>
+      </c>
+      <c r="C615" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F615" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="790">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15254,10 +15254,13 @@
       <c r="C596" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E596" s="1" t="s">
+      <c r="D596" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E596" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F596" s="1" t="s">
+      <c r="F596" s="16" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -14475,17 +14475,17 @@
       <c r="C558" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D558" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E558" s="16" t="s">
+      <c r="D558" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E558" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F558" s="16" t="s">
+      <c r="F558" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G558" s="22">
-        <v>46162</v>
+        <v>46181</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
@@ -14858,6 +14858,9 @@
       <c r="F575" s="9" t="s">
         <v>16</v>
       </c>
+      <c r="G575" s="22">
+        <v>46181</v>
+      </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A576" s="43">
@@ -14915,17 +14918,17 @@
       <c r="C578" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D578" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E578" s="16" t="s">
+      <c r="D578" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E578" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F578" s="16" t="s">
+      <c r="F578" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G578" s="22">
-        <v>46162</v>
+        <v>46181</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
@@ -15205,17 +15208,17 @@
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A594" s="44">
+      <c r="A594" s="43">
         <v>8073398709</v>
       </c>
-      <c r="B594" s="10" t="s">
+      <c r="B594" s="8" t="s">
         <v>761</v>
       </c>
-      <c r="C594" s="10" t="s">
-        <v>22</v>
+      <c r="C594" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>387</v>
+        <v>59</v>
       </c>
       <c r="F594" s="1" t="s">
         <v>16</v>
@@ -15337,14 +15340,17 @@
       <c r="C601" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D601" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E601" s="16" t="s">
+      <c r="D601" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E601" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="F601" s="16" t="s">
-        <v>16</v>
+      <c r="F601" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G601" s="22">
+        <v>46181</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
@@ -15445,7 +15451,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A609" s="47">
         <v>8076189717</v>
       </c>
@@ -15453,7 +15459,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A610" s="43">
         <v>8076260779</v>
       </c>
@@ -15463,17 +15469,20 @@
       <c r="C610" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D610" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E610" s="16" t="s">
+      <c r="D610" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E610" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F610" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F610" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G610" s="22">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A611" s="47">
         <v>8076298269</v>
       </c>
@@ -15481,7 +15490,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A612" s="47">
         <v>8076298033</v>
       </c>
@@ -15489,7 +15498,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A613" s="47">
         <v>8076291481</v>
       </c>
@@ -15497,7 +15506,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A614" s="47">
         <v>8076291122</v>
       </c>
@@ -15505,7 +15514,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A615" s="44">
         <v>8076953214</v>
       </c>
@@ -15522,7 +15531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A616" s="47">
         <v>8076958269</v>
       </c>
@@ -15530,7 +15539,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A617" s="47">
         <v>8076958509</v>
       </c>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="790">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15491,11 +15491,20 @@
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A612" s="47">
+      <c r="A612" s="43">
         <v>8076298033</v>
       </c>
-      <c r="B612" s="2" t="s">
+      <c r="B612" s="8" t="s">
         <v>784</v>
+      </c>
+      <c r="C612" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F612" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="790">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15541,11 +15541,20 @@
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A616" s="47">
+      <c r="A616" s="44">
         <v>8076958269</v>
       </c>
-      <c r="B616" s="2" t="s">
+      <c r="B616" s="10" t="s">
         <v>788</v>
+      </c>
+      <c r="C616" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="794">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2356,9 +2356,6 @@
     <t>1x3 W</t>
   </si>
   <si>
-    <t>Felipe Felizari</t>
-  </si>
-  <si>
     <t>OBRA</t>
   </si>
   <si>
@@ -2387,6 +2384,21 @@
   </si>
   <si>
     <t>JONAS RENATO SENS</t>
+  </si>
+  <si>
+    <t>JOSEANE CRISTINA TOBIAS</t>
+  </si>
+  <si>
+    <t>SILVANIO RAIMUNDO</t>
+  </si>
+  <si>
+    <t>JUAREZ SCHOTTEN</t>
+  </si>
+  <si>
+    <t>FELIPE FELIZARI</t>
+  </si>
+  <si>
+    <t>ADELMAR ARENDARTCHUK</t>
   </si>
 </sst>
 </file>
@@ -2451,7 +2463,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2491,6 +2503,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF33CC33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2582,7 +2600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2719,6 +2737,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3064,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I617"/>
+  <dimension ref="A1:I624"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -15361,7 +15382,7 @@
         <v>774</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>387</v>
@@ -15422,33 +15443,53 @@
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A606" s="44">
+      <c r="A606" s="11">
         <v>8076036211</v>
       </c>
-      <c r="B606" s="10" t="s">
+      <c r="B606" s="11" t="s">
         <v>777</v>
       </c>
-      <c r="C606" s="10" t="s">
+      <c r="C606" s="11"/>
+      <c r="D606" s="12"/>
+      <c r="E606" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F606" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A607" s="44">
+        <v>8077377580</v>
+      </c>
+      <c r="B607" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="C607" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F607" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A608" s="44">
+        <v>8076189679</v>
+      </c>
+      <c r="B608" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="E606" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F606" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B607" s="2" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A608" s="47">
-        <v>8076189679</v>
-      </c>
-      <c r="B608" s="2" t="s">
-        <v>781</v>
+      <c r="C608" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F608" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
@@ -15456,7 +15497,7 @@
         <v>8076189717</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
@@ -15487,7 +15528,7 @@
         <v>8076298269</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
@@ -15495,7 +15536,7 @@
         <v>8076298033</v>
       </c>
       <c r="B612" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C612" s="18" t="s">
         <v>7</v>
@@ -15512,7 +15553,7 @@
         <v>8076291481</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
@@ -15520,7 +15561,7 @@
         <v>8076291122</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
@@ -15528,7 +15569,7 @@
         <v>8076953214</v>
       </c>
       <c r="B615" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C615" s="10" t="s">
         <v>19</v>
@@ -15545,7 +15586,7 @@
         <v>8076958269</v>
       </c>
       <c r="B616" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C616" s="10" t="s">
         <v>19</v>
@@ -15562,7 +15603,69 @@
         <v>8076958509</v>
       </c>
       <c r="B617" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A618" s="56">
+        <v>8077892435</v>
+      </c>
+      <c r="B618" s="57" t="s">
         <v>789</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A619" s="56">
+        <v>8077892220</v>
+      </c>
+      <c r="B619" s="57" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A620" s="58">
+        <v>8077536205</v>
+      </c>
+      <c r="B620" s="20" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A621" s="47">
+        <v>8077370095</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A622" s="47">
+        <v>8076699602</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A623" s="47">
+        <v>8077371709</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A624" s="47">
+        <v>8077374578</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="794">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15524,11 +15524,20 @@
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A611" s="47">
+      <c r="A611" s="44">
         <v>8076298269</v>
       </c>
-      <c r="B611" s="2" t="s">
+      <c r="B611" s="10" t="s">
         <v>782</v>
+      </c>
+      <c r="C611" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F611" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
@@ -15549,11 +15558,20 @@
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A613" s="47">
+      <c r="A613" s="44">
         <v>8076291481</v>
       </c>
-      <c r="B613" s="2" t="s">
+      <c r="B613" s="10" t="s">
         <v>784</v>
+      </c>
+      <c r="C613" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F613" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="793">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2291,9 +2291,6 @@
   </si>
   <si>
     <t>MARIA LOURDES FUSINATO</t>
-  </si>
-  <si>
-    <t>beletti</t>
   </si>
   <si>
     <t>Maria Lourdes Fusinato</t>
@@ -3085,7 +3082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I624"/>
+  <dimension ref="A1:I622"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -12692,7 +12689,7 @@
         <v>46042</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.3">
@@ -14007,14 +14004,17 @@
       <c r="C533" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D533" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E533" s="16" t="s">
+      <c r="D533" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E533" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F533" s="16" t="s">
-        <v>16</v>
+      <c r="F533" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G533" s="22">
+        <v>46185</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
@@ -14167,7 +14167,7 @@
         <v>642</v>
       </c>
       <c r="C542" s="11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D542" s="11"/>
       <c r="E542" s="12" t="s">
@@ -14210,14 +14210,17 @@
       <c r="C544" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D544" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E544" s="16" t="s">
+      <c r="D544" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E544" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F544" s="16" t="s">
-        <v>16</v>
+      <c r="F544" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G544" s="22">
+        <v>46190</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
@@ -14230,8 +14233,8 @@
       <c r="C545" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D545" s="10" t="s">
-        <v>19</v>
+      <c r="D545" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E545" s="9" t="s">
         <v>116</v>
@@ -14240,7 +14243,7 @@
         <v>16</v>
       </c>
       <c r="G545" s="22">
-        <v>46139</v>
+        <v>46188</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
@@ -14251,7 +14254,7 @@
         <v>645</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -14903,7 +14906,7 @@
         <v>16</v>
       </c>
       <c r="G576" s="21" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
@@ -15037,7 +15040,7 @@
         <v>7</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>45</v>
@@ -15054,26 +15057,27 @@
         <v>22</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F584" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A585" s="44">
+      <c r="A585" s="41">
         <v>8067026793</v>
       </c>
-      <c r="B585" s="10" t="s">
+      <c r="B585" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="C585" s="10" t="s">
+      <c r="C585" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E585" s="1" t="s">
+      <c r="D585" s="11"/>
+      <c r="E585" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="F585" s="1" t="s">
+      <c r="F585" s="12" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15224,13 +15228,25 @@
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B593" s="2" t="s">
-        <v>758</v>
+      <c r="A593" s="43">
+        <v>8073398709</v>
+      </c>
+      <c r="B593" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="C593" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E593" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F593" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A594" s="43">
-        <v>8073398709</v>
+        <v>8073399555</v>
       </c>
       <c r="B594" s="8" t="s">
         <v>761</v>
@@ -15238,16 +15254,22 @@
       <c r="C594" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E594" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F594" s="1" t="s">
-        <v>16</v>
+      <c r="D594" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E594" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F594" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G594" s="22">
+        <v>46162</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A595" s="43">
-        <v>8073399555</v>
+        <v>8073784307</v>
       </c>
       <c r="B595" s="8" t="s">
         <v>762</v>
@@ -15259,133 +15281,139 @@
         <v>7</v>
       </c>
       <c r="E595" s="9" t="s">
-        <v>191</v>
+        <v>387</v>
       </c>
       <c r="F595" s="9" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G595" s="22">
-        <v>46162</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A596" s="43">
-        <v>8073784307</v>
+        <v>8073870779</v>
       </c>
       <c r="B596" s="8" t="s">
-        <v>763</v>
+        <v>247</v>
       </c>
       <c r="C596" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D596" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E596" s="16" t="s">
+      <c r="E596" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F596" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A597" s="41">
+        <v>8075220218</v>
+      </c>
+      <c r="B597" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="C597" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D597" s="11"/>
+      <c r="E597" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F597" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A598" s="43">
+        <v>8054198725</v>
+      </c>
+      <c r="B598" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C598" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D598" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E598" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F598" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A599" s="43">
+        <v>8073182347</v>
+      </c>
+      <c r="B599" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="C599" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D599" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E599" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="F599" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G599" s="22">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A600" s="44">
+        <v>8075397984</v>
+      </c>
+      <c r="B600" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C600" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="E600" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F596" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A597" s="43">
-        <v>8073870779</v>
-      </c>
-      <c r="B597" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C597" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E597" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F597" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A598" s="47">
-        <v>8074386445</v>
-      </c>
-      <c r="B598" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A599" s="41">
-        <v>8075220218</v>
-      </c>
-      <c r="B599" s="11" t="s">
-        <v>742</v>
-      </c>
-      <c r="C599" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D599" s="11"/>
-      <c r="E599" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F599" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A600" s="43">
-        <v>8054198725</v>
-      </c>
-      <c r="B600" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="C600" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D600" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E600" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F600" s="9" t="s">
+      <c r="F600" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A601" s="43">
-        <v>8073182347</v>
+        <v>8075507342</v>
       </c>
       <c r="B601" s="8" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C601" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D601" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E601" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="F601" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G601" s="22">
-        <v>46181</v>
+      <c r="E601" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F601" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A602" s="44">
-        <v>8075397984</v>
-      </c>
-      <c r="B602" s="10" t="s">
-        <v>774</v>
-      </c>
-      <c r="C602" s="10" t="s">
-        <v>779</v>
+      <c r="A602" s="43">
+        <v>8075464594</v>
+      </c>
+      <c r="B602" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C602" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>387</v>
+        <v>47</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>16</v>
@@ -15393,10 +15421,10 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A603" s="43">
-        <v>8075507342</v>
+        <v>8076034064</v>
       </c>
       <c r="B603" s="8" t="s">
-        <v>775</v>
+        <v>645</v>
       </c>
       <c r="C603" s="18" t="s">
         <v>7</v>
@@ -15409,280 +15437,246 @@
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A604" s="43">
-        <v>8075464594</v>
-      </c>
-      <c r="B604" s="8" t="s">
+      <c r="A604" s="11">
+        <v>8076036211</v>
+      </c>
+      <c r="B604" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="C604" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E604" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F604" s="1" t="s">
+      <c r="C604" s="11"/>
+      <c r="D604" s="12"/>
+      <c r="E604" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F604" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A605" s="43">
-        <v>8076034064</v>
-      </c>
-      <c r="B605" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="C605" s="18" t="s">
-        <v>7</v>
+      <c r="A605" s="44">
+        <v>8077377580</v>
+      </c>
+      <c r="B605" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="C605" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>222</v>
+        <v>422</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A606" s="11">
-        <v>8076036211</v>
-      </c>
-      <c r="B606" s="11" t="s">
-        <v>777</v>
-      </c>
-      <c r="C606" s="11"/>
-      <c r="D606" s="12"/>
-      <c r="E606" s="12" t="s">
+      <c r="A606" s="44">
+        <v>8076189679</v>
+      </c>
+      <c r="B606" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="C606" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F606" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A607" s="47">
+        <v>8076189717</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A608" s="43">
+        <v>8076260779</v>
+      </c>
+      <c r="B608" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="C608" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D608" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E608" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F606" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A607" s="44">
-        <v>8077377580</v>
-      </c>
-      <c r="B607" s="10" t="s">
-        <v>792</v>
-      </c>
-      <c r="C607" s="10" t="s">
+      <c r="F608" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G608" s="22">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A609" s="44">
+        <v>8076298269</v>
+      </c>
+      <c r="B609" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="C609" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E607" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="F607" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A608" s="44">
-        <v>8076189679</v>
-      </c>
-      <c r="B608" s="10" t="s">
-        <v>780</v>
-      </c>
-      <c r="C608" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E608" s="1" t="s">
+      <c r="E609" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F608" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A609" s="47">
-        <v>8076189717</v>
-      </c>
-      <c r="B609" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F609" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A610" s="43">
-        <v>8076260779</v>
+        <v>8076298033</v>
       </c>
       <c r="B610" s="8" t="s">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="C610" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D610" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E610" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F610" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G610" s="22">
-        <v>46181</v>
-      </c>
-    </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E610" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F610" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A611" s="44">
-        <v>8076298269</v>
+        <v>8076291481</v>
       </c>
       <c r="B611" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C611" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>387</v>
+        <v>222</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A612" s="43">
-        <v>8076298033</v>
-      </c>
-      <c r="B612" s="8" t="s">
-        <v>783</v>
-      </c>
-      <c r="C612" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E612" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F612" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A612" s="47">
+        <v>8076291122</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A613" s="44">
-        <v>8076291481</v>
+        <v>8076953214</v>
       </c>
       <c r="B613" s="10" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C613" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E613" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F613" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A614" s="44">
+        <v>8076958269</v>
+      </c>
+      <c r="B614" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="C614" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E614" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F613" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A614" s="47">
-        <v>8076291122</v>
-      </c>
-      <c r="B614" s="2" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A615" s="44">
-        <v>8076953214</v>
-      </c>
-      <c r="B615" s="10" t="s">
-        <v>786</v>
-      </c>
-      <c r="C615" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E615" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F615" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A616" s="44">
-        <v>8076958269</v>
-      </c>
-      <c r="B616" s="10" t="s">
+      <c r="F614" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A615" s="47">
+        <v>8076958509</v>
+      </c>
+      <c r="B615" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="C616" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E616" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F616" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A617" s="47">
-        <v>8076958509</v>
-      </c>
-      <c r="B617" s="2" t="s">
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A616" s="56">
+        <v>8077892435</v>
+      </c>
+      <c r="B616" s="57" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A618" s="56">
-        <v>8077892435</v>
-      </c>
-      <c r="B618" s="57" t="s">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A617" s="56">
+        <v>8077892220</v>
+      </c>
+      <c r="B617" s="57" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A619" s="56">
-        <v>8077892220</v>
-      </c>
-      <c r="B619" s="57" t="s">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A618" s="58">
+        <v>8077536205</v>
+      </c>
+      <c r="B618" s="20" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A620" s="58">
-        <v>8077536205</v>
-      </c>
-      <c r="B620" s="20" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A619" s="47">
+        <v>8077370095</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A620" s="47">
+        <v>8076699602</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A621" s="47">
-        <v>8077370095</v>
+        <v>8077371709</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A622" s="47">
-        <v>8076699602</v>
+        <v>8077374578</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A623" s="47">
-        <v>8077371709</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A624" s="47">
-        <v>8077374578</v>
-      </c>
-      <c r="B624" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="E624" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="E622" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F624" s="1" t="s">
+      <c r="F622" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -16718,7 +16712,7 @@
         <v>542</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="99" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -16860,7 +16854,7 @@
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="32" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C112" s="30" t="s">
         <v>542</v>
@@ -16871,7 +16865,7 @@
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="32" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C113" s="30" t="s">
         <v>542</v>
@@ -16882,7 +16876,7 @@
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C114" s="30" t="s">
         <v>542</v>
@@ -16890,7 +16884,7 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="32" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C115" s="30" t="s">
         <v>542</v>
@@ -19115,7 +19109,7 @@
         <v>8073398709</v>
       </c>
       <c r="B254" s="52" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19123,7 +19117,7 @@
         <v>8073399555</v>
       </c>
       <c r="B255" s="52" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19131,7 +19125,7 @@
         <v>8073784307</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19163,7 +19157,7 @@
         <v>8074386445</v>
       </c>
       <c r="B260" s="52" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="797">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2396,6 +2396,18 @@
   </si>
   <si>
     <t>ADELMAR ARENDARTCHUK</t>
+  </si>
+  <si>
+    <t>FATIMA BATISTI</t>
+  </si>
+  <si>
+    <t>JOSE ALDORI MONTEIRO DA COSTA</t>
+  </si>
+  <si>
+    <t>VALDIR MANNRICH</t>
+  </si>
+  <si>
+    <t>APARECIDA VICENTINI</t>
   </si>
 </sst>
 </file>
@@ -3082,7 +3094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I622"/>
+  <dimension ref="A1:I626"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -15460,7 +15472,7 @@
         <v>791</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>422</v>
@@ -15678,6 +15690,38 @@
       </c>
       <c r="F622" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A623" s="47">
+        <v>8077910394</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A624" s="47">
+        <v>8078241466</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A625" s="47">
+        <v>8078296373</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A626" s="47">
+        <v>8078371315</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -15482,14 +15482,14 @@
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A606" s="44">
+      <c r="A606" s="43">
         <v>8076189679</v>
       </c>
-      <c r="B606" s="10" t="s">
+      <c r="B606" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="C606" s="10" t="s">
-        <v>19</v>
+      <c r="C606" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>387</v>
@@ -15530,14 +15530,14 @@
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A609" s="44">
+      <c r="A609" s="43">
         <v>8076298269</v>
       </c>
-      <c r="B609" s="10" t="s">
+      <c r="B609" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="C609" s="10" t="s">
-        <v>19</v>
+      <c r="C609" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E609" s="1" t="s">
         <v>387</v>
@@ -15564,14 +15564,14 @@
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A611" s="44">
+      <c r="A611" s="43">
         <v>8076291481</v>
       </c>
-      <c r="B611" s="10" t="s">
+      <c r="B611" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="C611" s="10" t="s">
-        <v>19</v>
+      <c r="C611" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E611" s="1" t="s">
         <v>222</v>
@@ -15589,14 +15589,14 @@
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A613" s="44">
+      <c r="A613" s="43">
         <v>8076953214</v>
       </c>
-      <c r="B613" s="10" t="s">
+      <c r="B613" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="C613" s="10" t="s">
-        <v>19</v>
+      <c r="C613" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E613" s="1" t="s">
         <v>59</v>
@@ -15606,14 +15606,14 @@
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A614" s="44">
+      <c r="A614" s="43">
         <v>8076958269</v>
       </c>
-      <c r="B614" s="10" t="s">
+      <c r="B614" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="C614" s="10" t="s">
-        <v>19</v>
+      <c r="C614" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E614" s="1" t="s">
         <v>222</v>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3444" uniqueCount="797">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2472,7 +2472,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2512,12 +2512,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF33CC33"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2609,7 +2603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2746,8 +2740,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -15631,23 +15623,41 @@
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A616" s="56">
+      <c r="A616" s="43">
         <v>8077892435</v>
       </c>
-      <c r="B616" s="57" t="s">
+      <c r="B616" s="8" t="s">
         <v>788</v>
       </c>
+      <c r="C616" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A617" s="56">
+      <c r="A617" s="44">
         <v>8077892220</v>
       </c>
-      <c r="B617" s="57" t="s">
+      <c r="B617" s="10" t="s">
         <v>789</v>
       </c>
+      <c r="C617" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F617" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A618" s="58">
+      <c r="A618" s="56">
         <v>8077536205</v>
       </c>
       <c r="B618" s="20" t="s">

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3444" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="812">
   <si>
     <t>Protocolo</t>
   </si>
@@ -2317,9 +2317,6 @@
     <t>Depois aumentar para 36</t>
   </si>
   <si>
-    <t>Repro</t>
-  </si>
-  <si>
     <t>Marlise vonboelmel</t>
   </si>
   <si>
@@ -2408,6 +2405,54 @@
   </si>
   <si>
     <t>APARECIDA VICENTINI</t>
+  </si>
+  <si>
+    <t>MAURICIO BLASIUS</t>
+  </si>
+  <si>
+    <t>mailon kkrochmay</t>
+  </si>
+  <si>
+    <t>jaime gemano petry</t>
+  </si>
+  <si>
+    <t>jona srenato</t>
+  </si>
+  <si>
+    <t>walter preis</t>
+  </si>
+  <si>
+    <t>aparevida vecentini</t>
+  </si>
+  <si>
+    <t>ademar arendartchu</t>
+  </si>
+  <si>
+    <t>daniel de godoi</t>
+  </si>
+  <si>
+    <t>silvanio raimundo</t>
+  </si>
+  <si>
+    <t>djonatan fortunato</t>
+  </si>
+  <si>
+    <t>altair eugenio</t>
+  </si>
+  <si>
+    <t>antonio cirilo fernandes</t>
+  </si>
+  <si>
+    <t>sergio locks</t>
+  </si>
+  <si>
+    <t>valmor beletti</t>
+  </si>
+  <si>
+    <t>falta foto disjuntor</t>
+  </si>
+  <si>
+    <t>aprovado 6 instalado 3/ trocar disjuntor do cliente</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2517,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2512,6 +2557,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF33CC33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2603,7 +2654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2741,6 +2792,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3086,7 +3138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I626"/>
+  <dimension ref="A1:I627"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="47" bestFit="1" customWidth="1"/>
@@ -14171,7 +14223,7 @@
         <v>642</v>
       </c>
       <c r="C542" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D542" s="11"/>
       <c r="E542" s="12" t="s">
@@ -14258,7 +14310,7 @@
         <v>645</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -15044,7 +15096,7 @@
         <v>7</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>45</v>
@@ -15221,14 +15273,17 @@
       <c r="C592" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D592" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E592" s="16" t="s">
+      <c r="D592" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E592" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F592" s="16" t="s">
-        <v>16</v>
+      <c r="F592" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G592" s="22">
+        <v>46191</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
@@ -15241,10 +15296,13 @@
       <c r="C593" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E593" s="1" t="s">
+      <c r="D593" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E593" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F593" s="1" t="s">
+      <c r="F593" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15354,7 +15412,7 @@
         <v>8073182347</v>
       </c>
       <c r="B599" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C599" s="18" t="s">
         <v>7</v>
@@ -15363,7 +15421,7 @@
         <v>7</v>
       </c>
       <c r="E599" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F599" s="9" t="s">
         <v>16</v>
@@ -15377,10 +15435,10 @@
         <v>8075397984</v>
       </c>
       <c r="B600" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E600" s="1" t="s">
         <v>387</v>
@@ -15394,7 +15452,7 @@
         <v>8075507342</v>
       </c>
       <c r="B601" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C601" s="18" t="s">
         <v>7</v>
@@ -15411,7 +15469,7 @@
         <v>8075464594</v>
       </c>
       <c r="B602" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C602" s="18" t="s">
         <v>7</v>
@@ -15445,7 +15503,7 @@
         <v>8076036211</v>
       </c>
       <c r="B604" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C604" s="11"/>
       <c r="D604" s="12"/>
@@ -15461,10 +15519,10 @@
         <v>8077377580</v>
       </c>
       <c r="B605" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>422</v>
@@ -15478,15 +15536,18 @@
         <v>8076189679</v>
       </c>
       <c r="B606" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C606" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E606" s="1" t="s">
+      <c r="D606" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E606" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F606" s="1" t="s">
+      <c r="F606" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15495,7 +15556,7 @@
         <v>8076189717</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
@@ -15526,15 +15587,18 @@
         <v>8076298269</v>
       </c>
       <c r="B609" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C609" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E609" s="1" t="s">
+      <c r="D609" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E609" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F609" s="1" t="s">
+      <c r="F609" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15543,15 +15607,18 @@
         <v>8076298033</v>
       </c>
       <c r="B610" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C610" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E610" s="1" t="s">
+      <c r="D610" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E610" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="F610" s="1" t="s">
+      <c r="F610" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15560,7 +15627,7 @@
         <v>8076291481</v>
       </c>
       <c r="B611" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C611" s="18" t="s">
         <v>7</v>
@@ -15577,7 +15644,7 @@
         <v>8076291122</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.3">
@@ -15585,7 +15652,7 @@
         <v>8076953214</v>
       </c>
       <c r="B613" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C613" s="18" t="s">
         <v>7</v>
@@ -15602,12 +15669,15 @@
         <v>8076958269</v>
       </c>
       <c r="B614" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C614" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E614" s="1" t="s">
+      <c r="D614" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E614" s="16" t="s">
         <v>222</v>
       </c>
       <c r="F614" s="1" t="s">
@@ -15618,8 +15688,8 @@
       <c r="A615" s="47">
         <v>8076958509</v>
       </c>
-      <c r="B615" s="2" t="s">
-        <v>787</v>
+      <c r="B615" s="57" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
@@ -15627,7 +15697,7 @@
         <v>8077892435</v>
       </c>
       <c r="B616" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C616" s="18" t="s">
         <v>7</v>
@@ -15640,14 +15710,14 @@
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A617" s="44">
+      <c r="A617" s="43">
         <v>8077892220</v>
       </c>
-      <c r="B617" s="10" t="s">
-        <v>789</v>
-      </c>
-      <c r="C617" s="10" t="s">
-        <v>19</v>
+      <c r="B617" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="C617" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="E617" s="1" t="s">
         <v>387</v>
@@ -15661,7 +15731,7 @@
         <v>8077536205</v>
       </c>
       <c r="B618" s="20" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
@@ -15676,8 +15746,8 @@
       <c r="A620" s="47">
         <v>8076699602</v>
       </c>
-      <c r="B620" s="2" t="s">
-        <v>792</v>
+      <c r="B620" s="57" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
@@ -15693,7 +15763,7 @@
         <v>8077374578</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E622" s="1" t="s">
         <v>55</v>
@@ -15707,7 +15777,7 @@
         <v>8077910394</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
@@ -15715,23 +15785,40 @@
         <v>8078241466</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A625" s="47">
         <v>8078296373</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A626" s="47">
         <v>8078371315</v>
       </c>
-      <c r="B626" s="2" t="s">
+      <c r="B626" s="57" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A627" s="44">
+        <v>8078727979</v>
+      </c>
+      <c r="B627" s="10" t="s">
         <v>796</v>
+      </c>
+      <c r="C627" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15742,7 +15829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="32" bestFit="1" customWidth="1"/>
@@ -16766,7 +16853,7 @@
         <v>542</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>766</v>
+        <v>542</v>
       </c>
     </row>
     <row r="99" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -16820,6 +16907,9 @@
       <c r="C103" s="30" t="s">
         <v>542</v>
       </c>
+      <c r="D103" s="30" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="32" t="s">
@@ -16883,6 +16973,9 @@
       <c r="C109" s="30" t="s">
         <v>542</v>
       </c>
+      <c r="D109" s="30" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="32" t="s">
@@ -16919,7 +17012,7 @@
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="32" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C113" s="30" t="s">
         <v>542</v>
@@ -16930,20 +17023,130 @@
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="32" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C114" s="30" t="s">
         <v>542</v>
       </c>
+      <c r="D114" s="30" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C115" s="30" t="s">
         <v>542</v>
       </c>
       <c r="D115" s="30" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="32" t="s">
+        <v>797</v>
+      </c>
+      <c r="C116" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D116" s="30" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" s="32" t="s">
+        <v>798</v>
+      </c>
+      <c r="C117" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D117" s="30" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" s="32" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B119" s="32" t="s">
+        <v>800</v>
+      </c>
+      <c r="C119" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D119" s="30" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B120" s="32" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" s="32" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B122" s="32" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B123" s="32" t="s">
+        <v>804</v>
+      </c>
+      <c r="C123" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D123" s="30" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B124" s="32" t="s">
+        <v>805</v>
+      </c>
+      <c r="C124" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D124" s="30" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="32" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" s="32" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B127" s="32" t="s">
+        <v>808</v>
+      </c>
+      <c r="C127" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D127" s="30" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B128" s="32" t="s">
+        <v>809</v>
+      </c>
+      <c r="C128" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="D128" s="30" t="s">
         <v>542</v>
       </c>
     </row>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -13256,19 +13256,20 @@
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A496" s="44">
+      <c r="A496" s="41">
         <v>8062565978</v>
       </c>
-      <c r="B496" s="10" t="s">
+      <c r="B496" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="C496" s="6" t="s">
+      <c r="C496" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E496" s="1" t="s">
+      <c r="D496" s="11"/>
+      <c r="E496" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F496" s="1" t="s">
+      <c r="F496" s="12" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Projetos100125-Paulo.xlsx
+++ b/Projetos100125-Paulo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="812">
   <si>
     <t>Protocolo</t>
   </si>
@@ -15658,10 +15658,13 @@
       <c r="C613" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E613" s="1" t="s">
+      <c r="D613" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E613" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F613" s="1" t="s">
+      <c r="F613" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -15681,7 +15684,7 @@
       <c r="E614" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="F614" s="1" t="s">
+      <c r="F614" s="16" t="s">
         <v>16</v>
       </c>
     </row>
